--- a/TreinoOficial.xlsx
+++ b/TreinoOficial.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="93">
   <si>
     <t>Carimbo de data/hora</t>
   </si>
@@ -275,6 +275,21 @@
   </si>
   <si>
     <t xml:space="preserve">Pedro da Silva Santos </t>
+  </si>
+  <si>
+    <t>Matheus Felipe Ferreira</t>
+  </si>
+  <si>
+    <t>Jaciro Pedro Vaz Filho</t>
+  </si>
+  <si>
+    <t>Amilton Flávio de Araújo</t>
+  </si>
+  <si>
+    <t>Sandra Regina Simão de Brito Araújo</t>
+  </si>
+  <si>
+    <t>Rosedelma Fernandes Costa Vaz</t>
   </si>
 </sst>
 </file>
@@ -418,7 +433,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:D85" displayName="Form_Responses" name="Form_Responses" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:D90" displayName="Form_Responses" name="Form_Responses" id="1">
   <tableColumns count="4">
     <tableColumn name="Carimbo de data/hora" id="1"/>
     <tableColumn name="Nome Completo" id="2"/>
@@ -1826,6 +1841,76 @@
         <v>5</v>
       </c>
     </row>
+    <row r="86" ht="22.5" customHeight="1">
+      <c r="A86" s="6">
+        <v>46172.42073362268</v>
+      </c>
+      <c r="B86" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C86" s="8">
+        <v>38768.0</v>
+      </c>
+      <c r="D86" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="87" ht="22.5" customHeight="1">
+      <c r="A87" s="6">
+        <v>46172.42195447917</v>
+      </c>
+      <c r="B87" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C87" s="8">
+        <v>23486.0</v>
+      </c>
+      <c r="D87" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="88" ht="22.5" customHeight="1">
+      <c r="A88" s="6">
+        <v>46172.42239486111</v>
+      </c>
+      <c r="B88" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C88" s="8">
+        <v>28246.0</v>
+      </c>
+      <c r="D88" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="89" ht="22.5" customHeight="1">
+      <c r="A89" s="6">
+        <v>46172.42306185185</v>
+      </c>
+      <c r="B89" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C89" s="8">
+        <v>26769.0</v>
+      </c>
+      <c r="D89" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" ht="22.5" customHeight="1">
+      <c r="A90" s="6">
+        <v>46172.42366972222</v>
+      </c>
+      <c r="B90" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="C90" s="8">
+        <v>26191.0</v>
+      </c>
+      <c r="D90" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions gridLines="1" horizontalCentered="1"/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.25" right="0.25" top="0.75"/>

--- a/TreinoOficial.xlsx
+++ b/TreinoOficial.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="113">
   <si>
     <t>Carimbo de data/hora</t>
   </si>
@@ -290,6 +290,66 @@
   </si>
   <si>
     <t>Rosedelma Fernandes Costa Vaz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leandro de Lima Felipe </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ricardo Costa Divino </t>
+  </si>
+  <si>
+    <t>Maria Eduarda Oliveira de Souza</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adriano melo de jesus </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Irene da Silva Barros </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maria Graciele Correa da Silva </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luciana Alves Gomes da Silva </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thaís Nayra Lopes Santos </t>
+  </si>
+  <si>
+    <t xml:space="preserve">José Roberto Da Silva </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maria Madalena José da Silva </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Janete dos Santos Silva loiola </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alana Santos dos Reis </t>
+  </si>
+  <si>
+    <t>larissa cristina monteiro cei</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jocimara Ribeiro da Silva </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jessica Rauana Gomes dos Santos </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cibele Monteiro </t>
+  </si>
+  <si>
+    <t>Gisele Carrasco Munhoz SantAnna</t>
+  </si>
+  <si>
+    <t>Carllus vinicius da cruz bandeira</t>
+  </si>
+  <si>
+    <t>Gisele Fuzineli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antônio Marcos Ferreira de Souza </t>
   </si>
 </sst>
 </file>
@@ -433,7 +493,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:D90" displayName="Form_Responses" name="Form_Responses" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:D111" displayName="Form_Responses" name="Form_Responses" id="1">
   <tableColumns count="4">
     <tableColumn name="Carimbo de data/hora" id="1"/>
     <tableColumn name="Nome Completo" id="2"/>
@@ -1911,6 +1971,300 @@
         <v>5</v>
       </c>
     </row>
+    <row r="91" ht="22.5" customHeight="1">
+      <c r="A91" s="6">
+        <v>46172.618997847225</v>
+      </c>
+      <c r="B91" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C91" s="8">
+        <v>31472.0</v>
+      </c>
+      <c r="D91" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" ht="22.5" customHeight="1">
+      <c r="A92" s="6">
+        <v>46174.55289679398</v>
+      </c>
+      <c r="B92" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C92" s="8">
+        <v>28576.0</v>
+      </c>
+      <c r="D92" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="93" ht="22.5" customHeight="1">
+      <c r="A93" s="6">
+        <v>46174.554367372686</v>
+      </c>
+      <c r="B93" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="C93" s="8">
+        <v>39242.0</v>
+      </c>
+      <c r="D93" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="94" ht="22.5" customHeight="1">
+      <c r="A94" s="6">
+        <v>46174.55590923611</v>
+      </c>
+      <c r="B94" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="C94" s="8">
+        <v>46188.0</v>
+      </c>
+      <c r="D94" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" ht="22.5" customHeight="1">
+      <c r="A95" s="6">
+        <v>46174.55620152778</v>
+      </c>
+      <c r="B95" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="C95" s="8">
+        <v>25875.0</v>
+      </c>
+      <c r="D95" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="96" ht="22.5" customHeight="1">
+      <c r="A96" s="6">
+        <v>46174.60223347222</v>
+      </c>
+      <c r="B96" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="C96" s="8">
+        <v>32990.0</v>
+      </c>
+      <c r="D96" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="97" ht="22.5" customHeight="1">
+      <c r="A97" s="6">
+        <v>46174.62440346065</v>
+      </c>
+      <c r="B97" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C97" s="8">
+        <v>30162.0</v>
+      </c>
+      <c r="D97" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="98" ht="22.5" customHeight="1">
+      <c r="A98" s="6">
+        <v>46174.72185821759</v>
+      </c>
+      <c r="B98" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="C98" s="8">
+        <v>37443.0</v>
+      </c>
+      <c r="D98" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="99" ht="22.5" customHeight="1">
+      <c r="A99" s="6">
+        <v>46174.74487275463</v>
+      </c>
+      <c r="B99" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="C99" s="8">
+        <v>31323.0</v>
+      </c>
+      <c r="D99" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="100" ht="22.5" customHeight="1">
+      <c r="A100" s="6">
+        <v>46174.77712112269</v>
+      </c>
+      <c r="B100" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C100" s="8">
+        <v>24438.0</v>
+      </c>
+      <c r="D100" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" ht="22.5" customHeight="1">
+      <c r="A101" s="6">
+        <v>46175.276277303245</v>
+      </c>
+      <c r="B101" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="C101" s="8">
+        <v>30684.0</v>
+      </c>
+      <c r="D101" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" ht="22.5" customHeight="1">
+      <c r="A102" s="6">
+        <v>46175.74295688658</v>
+      </c>
+      <c r="B102" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="C102" s="8">
+        <v>38134.0</v>
+      </c>
+      <c r="D102" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="103" ht="22.5" customHeight="1">
+      <c r="A103" s="6">
+        <v>46176.623025810186</v>
+      </c>
+      <c r="B103" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="C103" s="8">
+        <v>32281.0</v>
+      </c>
+      <c r="D103" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="104" ht="22.5" customHeight="1">
+      <c r="A104" s="6">
+        <v>46178.65084480324</v>
+      </c>
+      <c r="B104" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="C104" s="8">
+        <v>32640.0</v>
+      </c>
+      <c r="D104" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="105" ht="22.5" customHeight="1">
+      <c r="A105" s="6">
+        <v>46178.652291736114</v>
+      </c>
+      <c r="B105" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="C105" s="8">
+        <v>34051.0</v>
+      </c>
+      <c r="D105" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="106" ht="22.5" customHeight="1">
+      <c r="A106" s="6">
+        <v>46178.65450200232</v>
+      </c>
+      <c r="B106" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="C106" s="8">
+        <v>30121.0</v>
+      </c>
+      <c r="D106" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="107" ht="22.5" customHeight="1">
+      <c r="A107" s="6">
+        <v>46178.760106539354</v>
+      </c>
+      <c r="B107" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C107" s="8">
+        <v>24772.0</v>
+      </c>
+      <c r="D107" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="108" ht="22.5" customHeight="1">
+      <c r="A108" s="6">
+        <v>46178.85085079861</v>
+      </c>
+      <c r="B108" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="C108" s="8">
+        <v>32252.0</v>
+      </c>
+      <c r="D108" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="109" ht="22.5" customHeight="1">
+      <c r="A109" s="6">
+        <v>46179.544264826385</v>
+      </c>
+      <c r="B109" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C109" s="8">
+        <v>38350.0</v>
+      </c>
+      <c r="D109" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="110" ht="22.5" customHeight="1">
+      <c r="A110" s="6">
+        <v>46179.817849803236</v>
+      </c>
+      <c r="B110" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="C110" s="8">
+        <v>28079.0</v>
+      </c>
+      <c r="D110" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="111" ht="22.5" customHeight="1">
+      <c r="A111" s="6">
+        <v>46179.81972917824</v>
+      </c>
+      <c r="B111" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="C111" s="8">
+        <v>26410.0</v>
+      </c>
+      <c r="D111" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions gridLines="1" horizontalCentered="1"/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.25" right="0.25" top="0.75"/>
